--- a/astro-site/public/dl/kit-tareas-pasteleria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/04-tareas-perfiles.xlsx
@@ -1,19 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Jefe Pastelero" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Pastelero" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ayudante" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dependiente Vitrina" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jefe Pastelero" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pastelero" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ayudante" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dependiente Vitrina" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Jefe Pastelero'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Pastelero'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Ayudante'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Dependiente Vitrina'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -93,6 +98,12 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -138,7 +149,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -160,64 +171,114 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="32">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="7" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="7" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -579,13 +640,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -593,6 +655,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -621,8 +684,24 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -631,18 +710,18 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -659,10 +738,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -702,18 +782,16 @@
           <t xml:space="preserve">  Inicio de Jornada</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="31" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -739,10 +817,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="31" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -768,10 +844,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="31" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -797,10 +871,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="31" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -826,10 +898,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -854,24 +924,23 @@
       <c r="F10" s="14" t="n"/>
       <c r="G10" s="15" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Producción</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
+      <c r="B12" s="29" t="n"/>
+      <c r="C12" s="29" t="n"/>
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="29" t="n"/>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="30" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="31" t="n">
+        <v>6</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -897,10 +966,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="31" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -926,10 +993,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="31" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -955,10 +1020,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="31" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -984,10 +1047,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="31" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1012,24 +1073,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Gestión</t>
         </is>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="17" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="31" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1055,10 +1115,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="31" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1084,10 +1142,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="31" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1113,10 +1169,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="31" t="n">
+        <v>14</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -1141,6 +1195,8 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
@@ -1149,7 +1205,7 @@
       </c>
       <c r="D26" s="19">
         <f>COUNTIF(F5:F24,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E26" s="20" t="inlineStr">
         <is>
@@ -1160,6 +1216,7 @@
         <v>14</v>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
@@ -1167,13 +1224,17 @@
         </is>
       </c>
       <c r="B28" s="15" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="30" t="n"/>
       <c r="E28" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F28" s="15" t="n"/>
-    </row>
+      <c r="G28" s="30" t="n"/>
+    </row>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
@@ -1193,11 +1254,20 @@
     <mergeCell ref="B28:D28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1206,18 +1276,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1234,10 +1304,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1277,18 +1348,16 @@
           <t xml:space="preserve">  Producción de Masas</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="31" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1314,10 +1383,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="31" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1343,10 +1410,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="31" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1372,10 +1437,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="31" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1401,10 +1464,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1430,10 +1491,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="31" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1458,24 +1517,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Elaboraciones</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="31" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1501,10 +1559,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="31" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1530,10 +1586,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="31" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1559,10 +1613,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="31" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1587,24 +1639,23 @@
       <c r="F17" s="14" t="n"/>
       <c r="G17" s="15" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Limpieza y Cierre</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="29" t="n"/>
+      <c r="F19" s="29" t="n"/>
+      <c r="G19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="31" t="n">
+        <v>11</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1630,10 +1681,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="31" t="n">
+        <v>12</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1659,10 +1708,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="31" t="n">
+        <v>13</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1687,6 +1734,8 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
@@ -1695,7 +1744,7 @@
       </c>
       <c r="D25" s="19">
         <f>COUNTIF(F5:F23,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
@@ -1706,6 +1755,7 @@
         <v>13</v>
       </c>
     </row>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
@@ -1713,13 +1763,17 @@
         </is>
       </c>
       <c r="B27" s="15" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="30" t="n"/>
       <c r="E27" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F27" s="15" t="n"/>
-    </row>
+      <c r="G27" s="30" t="n"/>
+    </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
@@ -1731,19 +1785,28 @@
   <mergeCells count="8">
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A13:G13"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A19:G19"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1752,18 +1815,18 @@
   <sheetPr>
     <tabColor rgb="004CAF50"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1780,10 +1843,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1823,18 +1887,16 @@
           <t xml:space="preserve">  Soporte a Producción</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="31" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1860,10 +1922,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="31" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1889,10 +1949,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="31" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1918,10 +1976,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="31" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1947,10 +2003,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1976,10 +2030,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="31" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2004,24 +2056,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Limpieza y Orden</t>
         </is>
       </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="23" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="23" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="31" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2047,10 +2098,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="31" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2076,10 +2125,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="31" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2105,10 +2152,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="31" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2134,10 +2179,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="31" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2162,6 +2205,8 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="n"/>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
@@ -2170,7 +2215,7 @@
       </c>
       <c r="D21" s="19">
         <f>COUNTIF(F5:F19,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E21" s="20" t="inlineStr">
         <is>
@@ -2181,6 +2226,7 @@
         <v>11</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
@@ -2188,13 +2234,17 @@
         </is>
       </c>
       <c r="B23" s="15" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="30" t="n"/>
       <c r="E23" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F23" s="15" t="n"/>
-    </row>
+      <c r="G23" s="30" t="n"/>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="21" t="inlineStr">
         <is>
@@ -2213,11 +2263,20 @@
     <mergeCell ref="B23:D23"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2226,18 +2285,18 @@
   <sheetPr>
     <tabColor rgb="002196F3"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2254,10 +2313,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2297,18 +2357,16 @@
           <t xml:space="preserve">  Apertura y Venta</t>
         </is>
       </c>
-      <c r="B5" s="26" t="n"/>
-      <c r="C5" s="26" t="n"/>
-      <c r="D5" s="26" t="n"/>
-      <c r="E5" s="26" t="n"/>
-      <c r="F5" s="26" t="n"/>
-      <c r="G5" s="26" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="31" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -2334,10 +2392,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="31" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -2363,10 +2419,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="31" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -2392,10 +2446,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="31" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -2421,10 +2473,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="31" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -2450,10 +2500,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="31" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -2478,24 +2526,23 @@
       <c r="F11" s="14" t="n"/>
       <c r="G11" s="15" t="n"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">  Mantenimiento y Cierre</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="26" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="29" t="n"/>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="31" t="n">
+        <v>7</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -2521,10 +2568,8 @@
       <c r="G14" s="15" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="31" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -2550,10 +2595,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="31" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -2579,10 +2622,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="31" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -2608,10 +2649,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="31" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -2637,10 +2676,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="31" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -2665,6 +2702,8 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="15" t="n"/>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
@@ -2673,7 +2712,7 @@
       </c>
       <c r="D22" s="19">
         <f>COUNTIF(F5:F20,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
@@ -2684,6 +2723,7 @@
         <v>12</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
@@ -2691,13 +2731,17 @@
         </is>
       </c>
       <c r="B24" s="15" t="n"/>
+      <c r="C24" s="29" t="n"/>
+      <c r="D24" s="30" t="n"/>
       <c r="E24" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F24" s="15" t="n"/>
-    </row>
+      <c r="G24" s="30" t="n"/>
+    </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
@@ -2716,10 +2760,19 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/04-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/04-tareas-perfiles.xlsx
@@ -278,6 +278,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -688,14 +698,15 @@
     <row r="9">
       <c r="B9" s="28" t="inlineStr">
         <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -712,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -767,7 +778,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1195,48 +1206,84 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25"/>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="31" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="14" t="n"/>
+      <c r="G27" s="15" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D26" s="19">
-        <f>COUNTIF(F5:F24,"✓")</f>
+      <c r="D29" s="19">
+        <f>COUNTIF(F5:F27,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E26" s="20" t="inlineStr">
+      <c r="E29" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F26" s="19" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="19" t="inlineStr">
+      <c r="F29" s="19">
+        <f>COUNTIF(B5:B27,"?*")</f>
+        <v>14.0</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n"/>
-      <c r="C28" s="29" t="n"/>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="19" t="inlineStr">
+      <c r="B31" s="15" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F28" s="15" t="n"/>
-      <c r="G28" s="30" t="n"/>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
+      <c r="F31" s="15" t="n"/>
+      <c r="G31" s="30" t="n"/>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1245,17 +1292,22 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F31:G31"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="F28:G28"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B28:D28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G27">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F13 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26 F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1278,7 +1330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1333,7 +1385,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1618,7 +1670,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Preparar pedidos especiales (tartas encargo)</t>
+          <t>Preparar pedidos especiales (tartas encargo) → 11 Control de Encargos · Ficha de Encargo</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1686,7 +1738,7 @@
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
-          <t>Guardar productos en cámara (etiquetar)</t>
+          <t>Guardar productos en cámara (etiquetar) → 13 Registro de Temperaturas · Etiquetas de Elaborado</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1734,48 +1786,84 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="14" t="n"/>
+      <c r="G24" s="15" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="31" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="14" t="n"/>
+      <c r="G25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="14" t="n"/>
+      <c r="G26" s="15" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D25" s="19">
-        <f>COUNTIF(F5:F23,"✓")</f>
+      <c r="D28" s="19">
+        <f>COUNTIF(F5:F26,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E25" s="20" t="inlineStr">
+      <c r="E28" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F25" s="19" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="19" t="inlineStr">
+      <c r="F28" s="19">
+        <f>COUNTIF(B5:B26,"?*")</f>
+        <v>13.0</v>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="19" t="inlineStr">
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="29" t="n"/>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="30" t="n"/>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="21" t="inlineStr">
+      <c r="F30" s="15" t="n"/>
+      <c r="G30" s="30" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1783,18 +1871,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="F27:G27"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A28:C28"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G26">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F20 F21 F22 F23 F24 F25 F26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1817,7 +1910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1872,7 +1965,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2205,48 +2298,84 @@
       <c r="F18" s="14" t="n"/>
       <c r="G18" s="15" t="n"/>
     </row>
-    <row r="19"/>
-    <row r="20"/>
+    <row r="19">
+      <c r="A19" s="31" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="14" t="n"/>
+      <c r="G19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
     <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D21" s="19">
-        <f>COUNTIF(F5:F19,"✓")</f>
+      <c r="D24" s="19">
+        <f>COUNTIF(F5:F22,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E21" s="20" t="inlineStr">
+      <c r="E24" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F21" s="19" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="19" t="inlineStr">
+      <c r="F24" s="19">
+        <f>COUNTIF(B5:B22,"?*")</f>
+        <v>11.0</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="19" t="inlineStr">
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="29" t="n"/>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F23" s="15" t="n"/>
-      <c r="G23" s="30" t="n"/>
-    </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="21" t="inlineStr">
+      <c r="F26" s="15" t="n"/>
+      <c r="G26" s="30" t="n"/>
+    </row>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2256,15 +2385,20 @@
   <mergeCells count="7">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="B26:D26"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="F26:G26"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G22">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2287,7 +2421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2342,7 +2476,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -2397,7 +2531,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Verificar etiquetas de alérgenos y precios</t>
+          <t>Verificar etiquetas de alérgenos y precios → 12 Control de Alérgenos de Vitrina</t>
         </is>
       </c>
       <c r="C7" s="27" t="inlineStr">
@@ -2451,7 +2585,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>Informar sobre ingredientes y alérgenos cuando pregunten</t>
+          <t>Informar sobre ingredientes y alérgenos cuando pregunten → 12 Control de Alérgenos de Vitrina</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
@@ -2478,7 +2612,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Gestionar pedidos de tartas personalizadas (rellenar ficha)</t>
+          <t>Gestionar pedidos de tartas personalizadas (rellenar ficha) → 11 Control de Encargos · Ficha de Encargo</t>
         </is>
       </c>
       <c r="C10" s="27" t="inlineStr">
@@ -2627,7 +2761,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Cierre de caja / cuadre de TPV</t>
+          <t>Cierre de caja / cuadre de TPV → 09 Apertura y Cierre de Caja</t>
         </is>
       </c>
       <c r="C17" s="27" t="inlineStr">
@@ -2702,48 +2836,84 @@
       <c r="F19" s="14" t="n"/>
       <c r="G19" s="15" t="n"/>
     </row>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="20">
+      <c r="A20" s="31" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="14" t="n"/>
+      <c r="G20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="14" t="n"/>
+      <c r="G21" s="15" t="n"/>
+    </row>
     <row r="22">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="31" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="14" t="n"/>
+      <c r="G22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="14" t="n"/>
+      <c r="G23" s="15" t="n"/>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D22" s="19">
-        <f>COUNTIF(F5:F20,"✓")</f>
+      <c r="D25" s="19">
+        <f>COUNTIF(F5:F23,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E22" s="20" t="inlineStr">
+      <c r="E25" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F22" s="19" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="F25" s="19">
+        <f>COUNTIF(B5:B23,"?*")</f>
+        <v>12.0</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n"/>
-      <c r="C24" s="29" t="n"/>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="19" t="inlineStr">
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F24" s="15" t="n"/>
-      <c r="G24" s="30" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="21" t="inlineStr">
+      <c r="F27" s="15" t="n"/>
+      <c r="G27" s="30" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2751,17 +2921,22 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F27:G27"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G23">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F14 F15 F16 F17 F18 F19 F20 F21 F22 F23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
